--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.73335670354663</v>
+        <v>7.106670464326328</v>
       </c>
       <c r="D2" t="n">
-        <v>34.93607341648083</v>
+        <v>5.677111930178135</v>
       </c>
       <c r="E2" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F2" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.50200433398334</v>
+        <v>3.494075704272293</v>
       </c>
       <c r="D3" t="n">
-        <v>19.33604778035502</v>
+        <v>3.142107764307691</v>
       </c>
       <c r="E3" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F3" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.4319400759055</v>
+        <v>3.645190262334645</v>
       </c>
       <c r="D4" t="n">
-        <v>21.34480362743968</v>
+        <v>3.468530589458948</v>
       </c>
       <c r="E4" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F4" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.08215053949288</v>
+        <v>5.538349462667593</v>
       </c>
       <c r="D5" t="n">
-        <v>25.62225595063791</v>
+        <v>4.163616591978661</v>
       </c>
       <c r="E5" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F5" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.01483193414239</v>
+        <v>6.014910189298138</v>
       </c>
       <c r="D6" t="n">
-        <v>35.8587056506213</v>
+        <v>5.827039668225961</v>
       </c>
       <c r="E6" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F6" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.3180408554683</v>
+        <v>2.001681639013598</v>
       </c>
       <c r="D7" t="n">
-        <v>11.60597851492889</v>
+        <v>1.885971508675945</v>
       </c>
       <c r="E7" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F7" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.0563916489355</v>
+        <v>6.021663642952018</v>
       </c>
       <c r="D8" t="n">
-        <v>35.85394613720285</v>
+        <v>5.826266247295464</v>
       </c>
       <c r="E8" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F8" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>58.59963886707271</v>
+        <v>9.522441315899316</v>
       </c>
       <c r="D9" t="n">
-        <v>57.38785284835686</v>
+        <v>9.325526087857991</v>
       </c>
       <c r="E9" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F9" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.89750923534331</v>
+        <v>8.108345250743287</v>
       </c>
       <c r="D10" t="n">
-        <v>48.89717579666313</v>
+        <v>7.945791066957758</v>
       </c>
       <c r="E10" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F10" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.4268887375552</v>
+        <v>7.381869419852721</v>
       </c>
       <c r="D11" t="n">
-        <v>44.62469964642035</v>
+        <v>7.251513692543306</v>
       </c>
       <c r="E11" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F11" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>71.91174638884407</v>
+        <v>11.68565878818716</v>
       </c>
       <c r="D12" t="n">
-        <v>70.75516313678607</v>
+        <v>11.49771400972774</v>
       </c>
       <c r="E12" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F12" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>58.69827636662824</v>
+        <v>9.53846990957709</v>
       </c>
       <c r="D13" t="n">
-        <v>57.8079778762521</v>
+        <v>9.393796404890965</v>
       </c>
       <c r="E13" t="n">
-        <v>16.61224094616655</v>
+        <v>2.699489153752066</v>
       </c>
       <c r="F13" t="n">
-        <v>17.06012953224883</v>
+        <v>2.772271048990435</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
